--- a/角色账号.xlsx
+++ b/角色账号.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
   <si>
     <t>角色</t>
   </si>
@@ -76,10 +76,10 @@
     <t>微信登录: code=dev_openid_13800000004</t>
   </si>
   <si>
-    <t>业主</t>
-  </si>
-  <si>
-    <t>res_001 (赵六)</t>
+    <t>平台管理员</t>
+  </si>
+  <si>
+    <t>res_admin01</t>
   </si>
   <si>
     <t>admin123456</t>
@@ -88,24 +88,6 @@
     <t>管理端登录</t>
   </si>
   <si>
-    <t>res_002 (钱七)</t>
-  </si>
-  <si>
-    <t>res_003 (孙八)</t>
-  </si>
-  <si>
-    <t>租户</t>
-  </si>
-  <si>
-    <t>res_004 (周九)</t>
-  </si>
-  <si>
-    <t>平台管理员</t>
-  </si>
-  <si>
-    <t>res_admin01</t>
-  </si>
-  <si>
     <t>物业管理员</t>
   </si>
   <si>
@@ -136,12 +118,27 @@
     <t>res_mch01 (陈老板)</t>
   </si>
   <si>
+    <t>res_mch02 (王老板)</t>
+  </si>
+  <si>
+    <t>res_mch03 (超市老板)</t>
+  </si>
+  <si>
+    <t>res_mch04 (农场老板)</t>
+  </si>
+  <si>
     <t>快递员</t>
   </si>
   <si>
     <t>res_courier01 (吴十)</t>
   </si>
   <si>
+    <t>res_courier02 (李四)</t>
+  </si>
+  <si>
+    <t>res_courier03 (王五)</t>
+  </si>
+  <si>
     <t>活动组长</t>
   </si>
   <si>
@@ -154,7 +151,7 @@
     <t>res_tech01 (刘师傅)</t>
   </si>
   <si>
-    <t>补充测试账号（8个，管理端测试用）：</t>
+    <t>测试账号</t>
   </si>
   <si>
     <t>姓名</t>
@@ -1124,7 +1121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.1111111111111" customWidth="1"/>
@@ -1227,7 +1224,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>13900000005</v>
+        <v>13800138000</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1238,13 +1235,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>13900000006</v>
+        <v>13900000001</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -1255,13 +1252,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>13900000010</v>
+        <v>13900000002</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -1272,13 +1269,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>13900000007</v>
+        <v>13900000003</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1289,13 +1286,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10">
-        <v>13800138000</v>
+        <v>13900000004</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -1306,13 +1303,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11">
-        <v>13900000001</v>
+        <v>13900000008</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -1326,10 +1323,10 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12">
-        <v>13900000002</v>
+        <v>13900000009</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1340,13 +1337,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13">
-        <v>13900000003</v>
+        <v>13900000017</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -1357,13 +1354,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
       <c r="C14">
-        <v>13900000004</v>
+        <v>13900000018</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -1374,13 +1371,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
       <c r="C15">
-        <v>13900000008</v>
+        <v>13900000016</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -1391,13 +1388,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16">
-        <v>13900000009</v>
+        <v>13900000013</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -1408,13 +1405,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C17">
-        <v>13900000011</v>
+        <v>13900000014</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -1425,13 +1422,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C18">
-        <v>13900000012</v>
+        <v>13900000011</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -1440,108 +1437,125 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>13900000012</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C26" t="s">
         <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>13911110001</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>13911110002</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>13911110003</v>
+        <v>13911110001</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>13911110004</v>
+        <v>13911110002</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>13911110005</v>
+        <v>13911110003</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>13911110006</v>
+        <v>13911110004</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>13911110007</v>
+        <v>13911110005</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
+        <v>13911110006</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>13911110007</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>13911110008</v>
       </c>
-      <c r="B32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" t="s">
-        <v>49</v>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
